--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/nuble.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M172"/>
+  <dimension ref="A1:M176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2220.27</v>
+        <v>2208.86</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2520.67</v>
+        <v>2495.51</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1603.23</v>
+        <v>1587.23</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1067.91</v>
+        <v>1056.01</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>745.55</v>
+        <v>741.46</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>745.84</v>
+        <v>744.89</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1471.21</v>
+        <v>1476.46</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2092.58</v>
+        <v>2115.34</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4527.12</v>
+        <v>4605.27</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2269.74</v>
+        <v>2265.72</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1153.45</v>
+        <v>1159.41</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2064.35</v>
+        <v>2078.92</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5064.91</v>
+        <v>5100.65</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>760.55</v>
+        <v>757.83</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2703.68</v>
+        <v>2693.99</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1840.17</v>
+        <v>1833.57</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5001.37</v>
+        <v>4997.35</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1155.76</v>
+        <v>1154.83</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1072.12</v>
+        <v>1071.26</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3131.06</v>
+        <v>3143.08</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>68337.89</v>
+        <v>68647.57000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2270.99</v>
+        <v>2281.28</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7451.12</v>
+        <v>7470.88</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2471.85</v>
+        <v>2475.02</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>6004.36</v>
+        <v>6055.67</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4622.6</v>
+        <v>4672.18</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2095.04</v>
+        <v>2106.5</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3675.25</v>
+        <v>3603.56</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2014.73</v>
+        <v>1967.6</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1034.72</v>
+        <v>1019.89</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>974.04</v>
+        <v>960.08</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2607.33</v>
+        <v>2569.76</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1730.72</v>
+        <v>1708.35</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>809.7</v>
+        <v>799.24</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>995.1799999999999</v>
+        <v>982.3200000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>867.23</v>
+        <v>865.52</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1238.64</v>
+        <v>1236.2</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1105.54</v>
+        <v>1103.37</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5654.78</v>
+        <v>5643.65</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1727.85</v>
+        <v>1717.02</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2757.16</v>
+        <v>2739.89</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2851.43</v>
+        <v>2833.56</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>998.71</v>
+        <v>992.46</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2828.11</v>
+        <v>2896.88</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1294.01</v>
+        <v>1333.25</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2119.06</v>
+        <v>2183.32</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>9929.48</v>
+        <v>10224.62</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>7127.45</v>
+        <v>7339.3</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1046.21</v>
+        <v>1077.31</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2268.95</v>
+        <v>2260.88</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3507.14</v>
+        <v>3480.89</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3625.87</v>
+        <v>3636.37</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3441.78</v>
+        <v>3473.08</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2955.27</v>
+        <v>2982.15</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3962.46</v>
+        <v>3997.75</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1081.58</v>
+        <v>1079.73</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>15840.61</v>
+        <v>15813.46</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>30212.46</v>
+        <v>30160.68</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>928.51</v>
+        <v>927.55</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2343.03</v>
+        <v>2340.61</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>16733.61</v>
+        <v>16642.48</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>907</v>
+        <v>902.0599999999999</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>9974.84</v>
+        <v>9914.23</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>12216.04</v>
+        <v>12168.89</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1512.4</v>
+        <v>1520.23</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>9124.139999999999</v>
+        <v>9132.93</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1415.08</v>
+        <v>1477.57</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>792.72</v>
+        <v>805.79</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4800.16</v>
+        <v>4811.97</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>14402.39</v>
+        <v>14300.75</v>
       </c>
     </row>
     <row r="72">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>803.28</v>
+        <v>797.61</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2724-156-CM26</t>
+          <t>4157-121-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4865,17 +4865,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I.Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.943.080-6</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2249.49</v>
+        <v>3271.73</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057510-1114-CM26</t>
+          <t>2724-156-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4926,17 +4926,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribuidora Colon </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.176.425-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2174.29</v>
+        <v>2239.44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4157-121-CM26</t>
+          <t>1057510-1114-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t xml:space="preserve">Distribuidora Colon </t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
+          <t>76.176.425-k</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3286.42</v>
+        <v>2164.57</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2298.36</v>
+        <v>2300.34</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>784.02</v>
+        <v>781.86</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1616.77</v>
+        <v>1592.65</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1334.4</v>
+        <v>1314.5</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>777.8</v>
+        <v>772.8200000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1481.79</v>
+        <v>1472.3</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>875.22</v>
+        <v>871.45</v>
       </c>
     </row>
     <row r="83">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1719.22</v>
+        <v>1685.32</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4157-176-CM26</t>
+          <t>1057506-3882-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5536,17 +5536,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1422.35</v>
+        <v>904.86</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1057506-3882-CM26</t>
+          <t>4157-176-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5597,17 +5597,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I.Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>929.33</v>
+        <v>1384.89</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1101.83</v>
+        <v>1081.85</v>
       </c>
     </row>
     <row r="87">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2896.89</v>
+        <v>2819.32</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1057510-1326-CM26</t>
+          <t>1057510-1327-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.283.950-2</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2534.51</v>
+        <v>860.54</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1057510-1327-CM26</t>
+          <t>1057510-1326-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>858.04</v>
+        <v>2541.89</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2402.19</v>
+        <v>2412.18</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1390.92</v>
+        <v>1396.7</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2115.57</v>
+        <v>2141.6</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1254.8</v>
+        <v>1271.5</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1719.77</v>
+        <v>1762.1</v>
       </c>
     </row>
     <row r="95">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1124.84</v>
+        <v>1152.52</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4596-237-CM26</t>
+          <t>1035180-16-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>77.283.950-2</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1074.71</v>
+        <v>1683.26</v>
       </c>
     </row>
     <row r="97">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2158.18</v>
+        <v>2198.99</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1035180-16-CM26</t>
+          <t>4596-237-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1652.02</v>
+        <v>1095.04</v>
       </c>
     </row>
     <row r="99">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1117.92</v>
+        <v>1130.63</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1062807-47-CM26</t>
+          <t>3747-111-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6512,17 +6512,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>RUSTIC PINK SPA</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>77.649.678-2</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2569.69</v>
+        <v>1644.57</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3901-82-CM26</t>
+          <t>1062807-47-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>RUSTIC PINK SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.649.678-2</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3842</v>
+        <v>2592.84</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3747-111-CM26</t>
+          <t>3901-82-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6634,17 +6634,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1629.89</v>
+        <v>3876.6</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1141.31</v>
+        <v>1148.61</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1168.63</v>
+        <v>1176.1</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>918.85</v>
+        <v>921.75</v>
       </c>
     </row>
     <row r="106">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2539.87</v>
+        <v>2547.86</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3904-323-CM26</t>
+          <t>1057511-579-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6939,17 +6939,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>936.63</v>
+        <v>809.36</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1057511-579-CM26</t>
+          <t>3904-323-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7000,17 +7000,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>806.02</v>
+        <v>940.51</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3747-114-CM26</t>
+          <t>1057510-1616-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>842.12</v>
+        <v>2050.68</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4596-256-CM26</t>
+          <t>1057510-1617-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>77.283.950-2</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>867.03</v>
+        <v>2564.42</v>
       </c>
     </row>
     <row r="111">
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>867.03</v>
+        <v>868.83</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4252-126-CM26</t>
+          <t>3747-114-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3295.54</v>
+        <v>843.86</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1057510-1616-CM26</t>
+          <t>4596-256-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2046.44</v>
+        <v>868.83</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1057510-1617-CM26</t>
+          <t>4252-126-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2559.12</v>
+        <v>3302.37</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3536.24</v>
+        <v>3521.05</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1228.57</v>
+        <v>1211.86</v>
       </c>
     </row>
     <row r="117">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1099.01</v>
+        <v>1111.3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4173-127-CM26</t>
+          <t>3590-79-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7610,17 +7610,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO LAGOS LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.547.396-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>926.27</v>
+        <v>1116.06</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3590-79-CM26</t>
+          <t>4173-126-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7671,17 +7671,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LIBRERÍA GIORGIO LAGOS LIMITADA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.547.396-7</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1111.85</v>
+        <v>838.78</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4173-126-CM26</t>
+          <t>4173-127-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>835.62</v>
+        <v>929.78</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5615-292-CM26</t>
+          <t>1060500-12-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>62.000.510-k</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES REGION DE NUBLE</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3303.15</v>
+        <v>2044.48</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1060500-12-CM26</t>
+          <t>5615-292-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>62.000.510-k</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES REGION DE NUBLE</t>
+          <t>I.Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2025.24</v>
+        <v>3334.53</v>
       </c>
     </row>
     <row r="123">
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>13060.15</v>
+        <v>12929.9</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1040758-70-CM26</t>
+          <t>1057514-182-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>61.607.006-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2201.33</v>
+        <v>1709.02</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1057514-182-CM26</t>
+          <t>1040758-70-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.607.006-1</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1727.82</v>
+        <v>2177.38</v>
       </c>
     </row>
     <row r="126">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4035.91</v>
+        <v>4055.73</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1043030-20-CM26</t>
+          <t>1011183-21-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>62.000.480-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Secretaria Ministerial de Educación Región Ñuble</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>COMERCIAL GMA SPA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
+          <t>77.053.654-5</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>5495.39</v>
+        <v>7150.94</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1011183-21-CM26</t>
+          <t>1043030-20-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.480-4</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Secretaria Ministerial de Educación Región Ñuble</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>COMERCIAL GMA SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>77.053.654-5</t>
+          <t>77.283.950-2</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>7128.25</v>
+        <v>5512.88</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1987.23</v>
+        <v>1997.79</v>
       </c>
     </row>
     <row r="130">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>974.3200000000001</v>
+        <v>985.75</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1057506-4120-CM26</t>
+          <t>4596-427-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1098.08</v>
+        <v>1779.1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4596-427-CM26</t>
+          <t>1057511-726-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1761.19</v>
+        <v>849.83</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4367-256-CM26</t>
+          <t>4367-257-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1249.8</v>
+        <v>819.63</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4367-257-CM26</t>
+          <t>1057506-4120-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.972.800-9</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO SALUD MUNICIPALIDAD DE QUILLON</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>811.38</v>
+        <v>1109.24</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1057511-726-CM26</t>
+          <t>4367-256-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>61.972.800-9</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>DEPARTAMENTO SALUD MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.283.950-2</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>841.27</v>
+        <v>1262.51</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1056.23</v>
+        <v>1066.14</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>12402.16</v>
+        <v>12518.48</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4522.44</v>
+        <v>4564.86</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>970.65</v>
+        <v>954.25</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>892.87</v>
+        <v>880.2</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1366.01</v>
+        <v>1347.24</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>995.26</v>
+        <v>981.59</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>986.59</v>
+        <v>980.47</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1507.19</v>
+        <v>1535.84</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>811.97</v>
+        <v>830.28</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2465.43</v>
+        <v>2521.04</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>4671.69</v>
+        <v>4777.05</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1692.98</v>
+        <v>1731.16</v>
       </c>
     </row>
     <row r="149">
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1084.22</v>
+        <v>1091.7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3784-309-CM26</t>
+          <t>3784-308-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>Papeles Cono Sur Ltda.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>78.437.580-3</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2561.18</v>
+        <v>1853.18</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3784-308-CM26</t>
+          <t>3784-309-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Papeles Cono Sur Ltda.</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>78.437.580-3</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1847.47</v>
+        <v>2569.1</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2866.11</v>
+        <v>2823.65</v>
       </c>
     </row>
     <row r="153">
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>4609.78</v>
+        <v>4515.04</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1233616-1153-CM26</t>
+          <t>1043030-31-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>62.000.480-4</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Secretaria Ministerial de Educación Región Ñuble</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>19124.36</v>
+        <v>993.33</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1043030-31-CM26</t>
+          <t>1233616-1153-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>62.000.480-4</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Secretaria Ministerial de Educación Región Ñuble</t>
+          <t>Servicio Local de Educación Pública Punilla Cordil</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>983.98</v>
+        <v>19306.02</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1285.79</v>
+        <v>1290.81</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>843</v>
+        <v>846.29</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>2135.23</v>
+        <v>2146.11</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>5141.73</v>
+        <v>5167.93</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2589.2</v>
+        <v>2599.28</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1144.75</v>
+        <v>1147.19</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>940.47</v>
+        <v>946.6</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>780.59</v>
+        <v>785.6799999999999</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>788.0599999999999</v>
+        <v>789.87</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1738.96</v>
+        <v>1733.47</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>773.61</v>
+        <v>772.0599999999999</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1047.73</v>
+        <v>1045.63</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>9376.82</v>
+        <v>9267.719999999999</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>772.73</v>
+        <v>768.45</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1713.76</v>
+        <v>1704.26</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>966.72</v>
+        <v>961.97</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,251 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2541.65</v>
+        <v>2558.66</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>4173-224-CM26</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>69.140.100-6</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Quirihue</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>798.6</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1057510-3114-CM26</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>61.607.002-9</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>2485.21</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2727-693-CM26</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>BLUE MIX SPA</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>1507.22</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>4352-22-CM26</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>69.141.400-0</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>4763.79</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/nuble.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M420"/>
+  <dimension ref="A1:M437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1205,7 +1205,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3659-23-CM25</t>
+          <t>3673-6-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>982.99</v>
+        <v>3295.47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3785-13-CM25</t>
+          <t>1057511-88-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1286,17 +1286,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1306,32 +1306,28 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.041.579-0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>13981.6</v>
+        <v>920.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3673-6-CM25</t>
+          <t>3785-13-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1356,12 +1352,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1371,28 +1367,32 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3295.47</v>
+        <v>13981.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1057511-88-CM25</t>
+          <t>3659-23-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1412,17 +1412,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.041.579-0</t>
+          <t>77.283.950-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>920.72</v>
+        <v>982.99</v>
       </c>
     </row>
     <row r="17">
@@ -2469,7 +2469,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3746-10-CM25</t>
+          <t>3746-11-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2563.55</v>
+        <v>3917.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3746-11-CM25</t>
+          <t>3746-10-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3917.9</v>
+        <v>2563.55</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1079580-30-CM25</t>
+          <t>3746-12-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2631,32 +2631,28 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t xml:space="preserve">Distribuidora Colon </t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.176.425-k</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>15392.92</v>
+        <v>3757.39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3746-12-CM25</t>
+          <t>3746-13-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,13 +2707,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3757.39</v>
+        <v>2012.76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3746-13-CM25</t>
+          <t>1079580-30-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2737,17 +2733,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2757,22 +2753,26 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribuidora Colon </t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.176.425-k</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2012.76</v>
+        <v>15392.92</v>
       </c>
     </row>
     <row r="38">
@@ -3457,7 +3457,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3784-2585-CM25</t>
+          <t>229-154-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3477,17 +3477,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3497,12 +3497,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SCANNO SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.055.785-2</t>
+          <t>76.041.579-0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3512,13 +3512,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2703.34</v>
+        <v>16960.08</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>229-154-CM25</t>
+          <t>3784-2585-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3538,17 +3538,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
+          <t>SCANNO SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.041.579-0</t>
+          <t>77.055.785-2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>16960.08</v>
+        <v>2703.34</v>
       </c>
     </row>
     <row r="51">
@@ -4404,7 +4404,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3904-281-CM25</t>
+          <t>3590-53-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4424,17 +4424,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4463,13 +4463,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>836.77</v>
+        <v>1943.06</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3590-53-CM25</t>
+          <t>3904-281-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4489,17 +4489,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4528,13 +4528,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1943.06</v>
+        <v>836.77</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2724-804-CM25</t>
+          <t>2724-805-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>SCANNO SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
+          <t>77.055.785-2</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4589,13 +4589,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2841.66</v>
+        <v>1508.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2724-805-CM25</t>
+          <t>2724-804-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SCANNO SPA</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.055.785-2</t>
+          <t>76.943.080-6</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1508.3</v>
+        <v>2841.66</v>
       </c>
     </row>
     <row r="68">
@@ -5611,7 +5611,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1057512-592-CM25</t>
+          <t>1057512-594-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5651,28 +5651,32 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1589.44</v>
+        <v>755.83</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1057513-310-CM25</t>
+          <t>1057512-592-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5697,12 +5701,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.607.005-3</t>
+          <t>61.607.004-5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5712,12 +5716,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
+          <t>76.943.080-6</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5727,13 +5731,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3597.58</v>
+        <v>1589.44</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1057512-594-CM25</t>
+          <t>1057513-310-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5758,12 +5762,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.607.004-5</t>
+          <t>61.607.005-3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5773,26 +5777,22 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>755.83</v>
+        <v>3597.58</v>
       </c>
     </row>
     <row r="86">
@@ -6290,7 +6290,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3497-225-CM25</t>
+          <t>3497-224-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6349,13 +6349,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1829.12</v>
+        <v>3755</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3497-226-CM25</t>
+          <t>3497-225-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6395,28 +6395,32 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2218.37</v>
+        <v>1829.12</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3497-224-CM25</t>
+          <t>3497-226-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6456,32 +6460,28 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3755</v>
+        <v>2218.37</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1233616-6855-CM25</t>
+          <t>1233616-6847-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6521,28 +6521,32 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>745.09</v>
+        <v>760.76</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1233616-6847-CM25</t>
+          <t>1233616-6855-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6582,26 +6586,22 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.943.080-6</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>760.76</v>
+        <v>745.09</v>
       </c>
     </row>
     <row r="99">
@@ -6802,7 +6802,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3482-104-CM25</t>
+          <t>3747-156-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.962.200-6</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6842,28 +6842,32 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1830.24</v>
+        <v>1899.91</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3747-156-CM25</t>
+          <t>3482-104-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6888,12 +6892,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>61.962.200-6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6903,26 +6907,22 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1899.91</v>
+        <v>1830.24</v>
       </c>
     </row>
     <row r="104">
@@ -7115,7 +7115,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2727-397-CM25</t>
+          <t>4157-624-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7135,17 +7135,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7155,17 +7155,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7174,13 +7174,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2878.67</v>
+        <v>2510.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>4157-624-CM25</t>
+          <t>2727-397-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7200,17 +7200,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7220,17 +7220,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2510.6</v>
+        <v>2878.67</v>
       </c>
     </row>
     <row r="109">
@@ -7688,7 +7688,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4256-223-CM25</t>
+          <t>1052231-81-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7708,17 +7708,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7728,28 +7728,32 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Papeles Cono Sur Ltda.</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>78.437.580-3</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>813.74</v>
+        <v>4610.58</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1072229-60-CM25</t>
+          <t>4256-223-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7769,17 +7773,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7789,12 +7793,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
+          <t>Papeles Cono Sur Ltda.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.041.579-0</t>
+          <t>78.437.580-3</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7804,13 +7808,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>10134.58</v>
+        <v>813.74</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1052231-81-CM25</t>
+          <t>1072229-60-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7835,12 +7839,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7850,26 +7854,22 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.041.579-0</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>4610.58</v>
+        <v>10134.58</v>
       </c>
     </row>
     <row r="119">
@@ -8196,7 +8196,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4157-722-CM25</t>
+          <t>3904-875-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8221,12 +8221,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8236,12 +8236,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3217.4</v>
+        <v>739.66</v>
       </c>
     </row>
     <row r="125">
@@ -8322,7 +8322,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3904-875-CM25</t>
+          <t>4157-722-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>739.66</v>
+        <v>3217.4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1072229-69-CM25</t>
+          <t>3784-2782-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8427,17 +8427,17 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>738.72</v>
+        <v>2848.34</v>
       </c>
     </row>
     <row r="128">
@@ -8517,7 +8517,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3784-2782-CM25</t>
+          <t>1072229-69-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8557,17 +8557,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8576,7 +8576,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2848.34</v>
+        <v>738.72</v>
       </c>
     </row>
     <row r="130">
@@ -8769,7 +8769,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4173-170-CM25</t>
+          <t>1057510-5765-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8809,32 +8809,28 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.462.500-5</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1137.69</v>
+        <v>717.91</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1057510-5765-CM25</t>
+          <t>4173-170-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8859,12 +8855,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8874,22 +8870,26 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SURTI VENTAS S.A.</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.462.500-5</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr"/>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>717.91</v>
+        <v>1137.69</v>
       </c>
     </row>
     <row r="135">
@@ -9025,7 +9025,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2724-1179-CM25</t>
+          <t>2724-1180-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9065,28 +9065,32 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>INVERSIONES Y RENTAS AMINORTE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.432.149-9</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>764.39</v>
+        <v>2272.4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2724-1180-CM25</t>
+          <t>2724-1179-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9126,32 +9130,28 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>INVERSIONES Y RENTAS AMINORTE LIMITADA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.432.149-9</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2272.4</v>
+        <v>764.39</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1057506-2023-CM25</t>
+          <t>4173-172-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9171,17 +9171,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9191,12 +9191,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
+          <t>76.195.957-3</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -9206,13 +9206,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1015.82</v>
+        <v>1373.11</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4173-172-CM25</t>
+          <t>1057506-2023-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9232,17 +9232,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.195.957-3</t>
+          <t>76.943.080-6</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1373.11</v>
+        <v>1015.82</v>
       </c>
     </row>
     <row r="141">
@@ -9594,7 +9594,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1233616-7494-CM25</t>
+          <t>1233616-7495-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9653,13 +9653,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1641.05</v>
+        <v>720.75</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1233616-7495-CM25</t>
+          <t>1233616-7494-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9699,12 +9699,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9718,7 +9718,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>720.75</v>
+        <v>1641.05</v>
       </c>
     </row>
     <row r="148">
@@ -9854,7 +9854,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1072229-76-CM25</t>
+          <t>5615-636-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>CHICAUMA CHILE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.935.401-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9913,13 +9913,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1277.55</v>
+        <v>1137.88</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1043030-53-CM25</t>
+          <t>1072229-76-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9944,12 +9944,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>62.000.480-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9959,28 +9959,32 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
+          <t>CHICAUMA CHILE SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.195.957-3</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
+          <t>77.935.401-6</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1028.24</v>
+        <v>1277.55</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>4594-743-CM25</t>
+          <t>1043030-53-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10000,17 +10004,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>62.000.480-4</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10020,32 +10024,28 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.195.957-3</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>745.55</v>
+        <v>1028.24</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5615-636-CM25</t>
+          <t>4594-743-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10085,17 +10085,17 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10104,7 +10104,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1137.88</v>
+        <v>745.55</v>
       </c>
     </row>
     <row r="154">
@@ -10614,7 +10614,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1057512-1071-CM25</t>
+          <t>1057508-2444-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10639,12 +10639,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.607.004-5</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
+          <t>77.283.950-2</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10669,13 +10669,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>888.64</v>
+        <v>890.5</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1057508-2444-CM25</t>
+          <t>1057512-1071-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10700,12 +10700,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>61.607.004-5</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE YUNG</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10715,12 +10715,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
+          <t>76.943.080-6</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>890.5</v>
+        <v>888.64</v>
       </c>
     </row>
     <row r="164">
@@ -10923,7 +10923,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4256-668-CM25</t>
+          <t>1057509-25275-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10943,17 +10943,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>61.607.001-0</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10963,28 +10963,32 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Papeles Cono Sur Ltda.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>78.437.580-3</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1167.89</v>
+        <v>727.89</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1057509-25275-CM25</t>
+          <t>4256-668-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11004,17 +11008,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.607.001-0</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11024,26 +11028,22 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Papeles Cono Sur Ltda.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>78.437.580-3</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>727.89</v>
+        <v>1167.89</v>
       </c>
     </row>
     <row r="169">
@@ -11175,7 +11175,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4173-227-CM25</t>
+          <t>229-872-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11200,12 +11200,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11215,32 +11215,28 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1750.51</v>
+        <v>1849.97</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>229-872-CM25</t>
+          <t>4173-227-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11265,12 +11261,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11280,22 +11276,26 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1849.97</v>
+        <v>1750.51</v>
       </c>
     </row>
     <row r="173">
@@ -11427,7 +11427,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2724-1459-CM25</t>
+          <t>2724-1457-CM25</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11467,12 +11467,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11486,7 +11486,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>961.1799999999999</v>
+        <v>765.1900000000001</v>
       </c>
     </row>
     <row r="176">
@@ -11557,7 +11557,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2724-1457-CM25</t>
+          <t>2724-1459-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11597,12 +11597,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>93.558.000-5</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -11616,7 +11616,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>765.1900000000001</v>
+        <v>961.1799999999999</v>
       </c>
     </row>
     <row r="178">
@@ -11931,7 +11931,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>4252-332-CM25</t>
+          <t>1043046-102-CM25</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11956,12 +11956,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>62.000.450-2</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11971,32 +11971,28 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.205.722-9</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1348.93</v>
+        <v>724.4400000000001</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1043046-102-CM25</t>
+          <t>4252-332-CM25</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12021,12 +12017,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>62.000.450-2</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12036,22 +12032,26 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
+          <t>96.989.530-7</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>724.4400000000001</v>
+        <v>1348.93</v>
       </c>
     </row>
     <row r="185">
@@ -13012,7 +13012,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1057513-719-CM25</t>
+          <t>1059082-185-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13037,12 +13037,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.607.005-3</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13052,12 +13052,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -13071,13 +13071,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2078.92</v>
+        <v>8230.43</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1059082-185-CM25</t>
+          <t>1059082-186-CM25</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13117,32 +13117,28 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>8230.43</v>
+        <v>4308.11</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1059082-186-CM25</t>
+          <t>1059082-187-CM25</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13182,12 +13178,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
+          <t>99.533.780-0</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -13197,13 +13193,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>4308.11</v>
+        <v>3036.12</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1059082-187-CM25</t>
+          <t>1059082-188-CM25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13243,12 +13239,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
+          <t>76.943.080-6</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -13258,13 +13254,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>3036.12</v>
+        <v>4378.34</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1059082-188-CM25</t>
+          <t>1059082-189-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13304,28 +13300,32 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>4378.34</v>
+        <v>3887.64</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1059082-189-CM25</t>
+          <t>1049242-117-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13350,12 +13350,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.430-8</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13365,32 +13365,28 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3887.64</v>
+        <v>5100.65</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1049242-117-CM25</t>
+          <t>1057513-719-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13415,12 +13411,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>62.000.430-8</t>
+          <t>61.607.005-3</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13430,28 +13426,32 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>5100.65</v>
+        <v>2078.92</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1059082-193-CM25</t>
+          <t>1059082-191-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.195.957-3</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13506,7 +13506,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2413.13</v>
+        <v>1462.33</v>
       </c>
     </row>
     <row r="208">
@@ -13577,7 +13577,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1059082-191-CM25</t>
+          <t>1059082-193-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13617,12 +13617,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.195.957-3</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13632,13 +13632,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1462.33</v>
+        <v>2413.13</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1113562-25-CM25</t>
+          <t>1057510-7420-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13658,17 +13658,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13678,17 +13678,17 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -13697,7 +13697,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>757.83</v>
+        <v>1833.57</v>
       </c>
     </row>
     <row r="211">
@@ -13764,7 +13764,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1057510-7420-CM25</t>
+          <t>1113562-25-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13784,17 +13784,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13804,17 +13804,17 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -13823,7 +13823,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1833.57</v>
+        <v>757.83</v>
       </c>
     </row>
     <row r="213">
@@ -14650,7 +14650,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>5615-4-CM26</t>
+          <t>5615-5-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14690,28 +14690,32 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>960.08</v>
+        <v>1019.89</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5615-5-CM26</t>
+          <t>5615-4-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14751,26 +14755,22 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.943.080-6</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1019.89</v>
+        <v>960.08</v>
       </c>
     </row>
     <row r="228">
@@ -15284,7 +15284,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>4367-22-CM26</t>
+          <t>4367-23-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15324,28 +15324,32 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr"/>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1717.02</v>
+        <v>2739.89</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>4367-23-CM26</t>
+          <t>4367-22-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15385,32 +15389,28 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>2739.89</v>
+        <v>1717.02</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1700-1-CM26</t>
+          <t>3904-20-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15435,12 +15435,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15450,17 +15450,17 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -15469,13 +15469,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2833.56</v>
+        <v>992.46</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>3904-20-CM26</t>
+          <t>1700-1-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15500,12 +15500,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15515,17 +15515,17 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -15534,7 +15534,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>992.46</v>
+        <v>2833.56</v>
       </c>
     </row>
     <row r="240">
@@ -16186,7 +16186,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>3905-28-CM26</t>
+          <t>1079580-24-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16206,17 +16206,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>72.529.500-6</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PINTO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16226,12 +16226,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -16245,7 +16245,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1079.73</v>
+        <v>30160.68</v>
       </c>
     </row>
     <row r="251">
@@ -16312,7 +16312,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1079580-24-CM26</t>
+          <t>3905-28-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16332,17 +16332,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>72.529.500-6</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PINTO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16352,12 +16352,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -16371,13 +16371,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>30160.68</v>
+        <v>1079.73</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3784-87-CM26</t>
+          <t>3747-41-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16397,17 +16397,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16417,32 +16417,28 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>927.55</v>
+        <v>2340.61</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3747-41-CM26</t>
+          <t>3784-87-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16462,17 +16458,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16482,22 +16478,26 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr"/>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2340.61</v>
+        <v>927.55</v>
       </c>
     </row>
     <row r="255">
@@ -17527,7 +17527,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1057511-406-CM26</t>
+          <t>3904-169-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17547,17 +17547,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17586,13 +17586,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1314.5</v>
+        <v>1592.65</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3904-169-CM26</t>
+          <t>1057511-406-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17612,17 +17612,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17651,13 +17651,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1592.65</v>
+        <v>1314.5</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>4596-129-CM26</t>
+          <t>4596-130-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -17716,13 +17716,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>772.8200000000001</v>
+        <v>1472.3</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>4596-130-CM26</t>
+          <t>4596-129-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17742,7 +17742,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -17781,7 +17781,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1472.3</v>
+        <v>772.8200000000001</v>
       </c>
     </row>
     <row r="275">
@@ -18551,7 +18551,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1069417-314-CM26</t>
+          <t>4352-7-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18576,12 +18576,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18591,28 +18591,32 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>8214.35</v>
+        <v>2141.6</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>4352-7-CM26</t>
+          <t>1069417-314-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18637,12 +18641,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18652,32 +18656,28 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>2141.6</v>
+        <v>8214.35</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1069417-325-CM26</t>
+          <t>1057506-3922-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18702,12 +18702,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18717,28 +18717,32 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr"/>
+          <t>77.638.992-7</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1194.66</v>
+        <v>1271.5</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1057506-3922-CM26</t>
+          <t>1069417-325-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18763,12 +18767,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18778,32 +18782,28 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
-        </is>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1271.5</v>
+        <v>1194.66</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1035180-13-CM26</t>
+          <t>4157-235-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18823,17 +18823,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18843,28 +18843,32 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1762.1</v>
+        <v>1152.52</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>4157-235-CM26</t>
+          <t>1035180-13-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18884,17 +18888,17 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18904,32 +18908,28 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1152.52</v>
+        <v>1762.1</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1035180-16-CM26</t>
+          <t>1069417-365-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18949,17 +18949,17 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18969,28 +18969,32 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr"/>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1683.26</v>
+        <v>3473.23</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2724-275-CM26</t>
+          <t>4596-237-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19010,17 +19014,17 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19030,12 +19034,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -19049,13 +19053,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>2198.99</v>
+        <v>1095.04</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4596-237-CM26</t>
+          <t>2724-275-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19075,17 +19079,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19095,12 +19099,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -19114,13 +19118,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1095.04</v>
+        <v>2198.99</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1069417-365-CM26</t>
+          <t>1035180-16-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19140,17 +19144,17 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19160,26 +19164,22 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>3473.23</v>
+        <v>1683.26</v>
       </c>
     </row>
     <row r="297">
@@ -19250,7 +19250,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1062807-47-CM26</t>
+          <t>3747-111-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19270,17 +19270,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19290,17 +19290,17 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>RUSTIC PINK SPA</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>77.649.678-2</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -19309,7 +19309,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2592.84</v>
+        <v>1644.57</v>
       </c>
     </row>
     <row r="299">
@@ -19380,7 +19380,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>3747-111-CM26</t>
+          <t>1062807-47-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19400,17 +19400,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19420,17 +19420,17 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>RUSTIC PINK SPA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
+          <t>77.649.678-2</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -19439,13 +19439,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1644.57</v>
+        <v>2592.84</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1089561-4-CM26</t>
+          <t>3904-318-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19465,17 +19465,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19485,17 +19485,17 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -19504,13 +19504,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1148.61</v>
+        <v>1176.1</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>3904-318-CM26</t>
+          <t>1089561-4-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19530,17 +19530,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -19550,17 +19550,17 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -19569,13 +19569,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1176.1</v>
+        <v>1148.61</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>4364-180-CM26</t>
+          <t>4596-254-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19595,17 +19595,17 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>69.141.401-9</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -19615,12 +19615,12 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -19634,13 +19634,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>921.75</v>
+        <v>2547.86</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>4596-254-CM26</t>
+          <t>4364-180-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19660,17 +19660,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>69.141.401-9</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19680,12 +19680,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -19699,7 +19699,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>2547.86</v>
+        <v>921.75</v>
       </c>
     </row>
     <row r="305">
@@ -19835,7 +19835,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>3747-114-CM26</t>
+          <t>1057510-1617-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19860,12 +19860,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19875,32 +19875,28 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>843.86</v>
+        <v>2564.42</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>4596-256-CM26</t>
+          <t>4596-257-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19920,7 +19916,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -19965,7 +19961,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>4596-257-CM26</t>
+          <t>4596-256-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19985,7 +19981,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -20030,7 +20026,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>4252-126-CM26</t>
+          <t>3747-114-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20055,12 +20051,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -20070,17 +20066,17 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -20089,13 +20085,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>3302.37</v>
+        <v>843.86</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1057510-1616-CM26</t>
+          <t>4252-126-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20120,12 +20116,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -20135,17 +20131,17 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -20154,13 +20150,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2050.68</v>
+        <v>3302.37</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1057510-1617-CM26</t>
+          <t>1057510-1616-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20200,22 +20196,26 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K312" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2564.42</v>
+        <v>2050.68</v>
       </c>
     </row>
     <row r="313">
@@ -20347,7 +20347,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1057508-1639-CM26</t>
+          <t>1069417-454-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20367,17 +20367,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Comercial IBL SpA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>76.452.485-3</t>
+          <t>77.283.950-2</t>
         </is>
       </c>
       <c r="K315" t="inlineStr"/>
@@ -20402,13 +20402,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>858.72</v>
+        <v>1628.69</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1069417-454-CM26</t>
+          <t>1057508-1639-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20428,17 +20428,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
+          <t>76.452.485-3</t>
         </is>
       </c>
       <c r="K316" t="inlineStr"/>
@@ -20463,7 +20463,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1628.69</v>
+        <v>858.72</v>
       </c>
     </row>
     <row r="317">
@@ -20534,7 +20534,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>3590-79-CM26</t>
+          <t>4173-126-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -20554,17 +20554,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20574,17 +20574,17 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LIBRERÍA GIORGIO LAGOS LIMITADA</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.547.396-7</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -20593,13 +20593,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1116.06</v>
+        <v>838.78</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>4173-126-CM26</t>
+          <t>4173-127-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -20658,13 +20658,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>838.78</v>
+        <v>929.78</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>4173-127-CM26</t>
+          <t>3590-79-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -20684,17 +20684,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -20704,17 +20704,17 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO LAGOS LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>77.547.396-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -20723,13 +20723,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>929.78</v>
+        <v>1116.06</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1060500-12-CM26</t>
+          <t>5615-292-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -20754,12 +20754,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>62.000.510-k</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20769,17 +20769,17 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -20788,13 +20788,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>2044.48</v>
+        <v>3334.53</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>5615-292-CM26</t>
+          <t>1060500-12-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20819,12 +20819,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>62.000.510-k</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20834,17 +20834,17 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>3334.53</v>
+        <v>2044.48</v>
       </c>
     </row>
     <row r="323">
@@ -21050,7 +21050,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1059082-12-CM26</t>
+          <t>1069417-548-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21075,12 +21075,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21090,32 +21090,28 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
-        </is>
-      </c>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>960.8200000000001</v>
+        <v>1110.7</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1069417-548-CM26</t>
+          <t>1059082-12-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21140,12 +21136,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21155,22 +21151,26 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K327" t="inlineStr"/>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1110.7</v>
+        <v>960.8200000000001</v>
       </c>
     </row>
     <row r="328">
@@ -21241,7 +21241,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1043030-20-CM26</t>
+          <t>1011183-21-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21266,12 +21266,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>62.000.480-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21281,28 +21281,32 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>COMERCIAL GMA SPA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr"/>
+          <t>77.053.654-5</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>5512.88</v>
+        <v>7150.94</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1011183-21-CM26</t>
+          <t>1043030-20-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21327,12 +21331,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.480-4</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21342,26 +21346,22 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>COMERCIAL GMA SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>77.053.654-5</t>
-        </is>
-      </c>
-      <c r="K330" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr"/>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>7150.94</v>
+        <v>5512.88</v>
       </c>
     </row>
     <row r="331">
@@ -21497,7 +21497,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1057506-4120-CM26</t>
+          <t>4367-256-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21522,12 +21522,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>61.972.800-9</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21537,32 +21537,28 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr"/>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>1109.24</v>
+        <v>1262.51</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>4596-427-CM26</t>
+          <t>1057511-726-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21587,12 +21583,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21602,12 +21598,12 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -21621,13 +21617,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1779.1</v>
+        <v>849.83</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>4367-256-CM26</t>
+          <t>1057506-4120-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21652,12 +21648,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.972.800-9</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -21667,28 +21663,32 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1262.51</v>
+        <v>1109.24</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>4367-257-CM26</t>
+          <t>4596-427-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -21713,12 +21713,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.972.800-9</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21728,17 +21728,17 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -21747,13 +21747,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>819.63</v>
+        <v>1779.1</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1057511-726-CM26</t>
+          <t>4367-257-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -21778,12 +21778,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>61.972.800-9</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21793,17 +21793,17 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -21812,13 +21812,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>849.83</v>
+        <v>819.63</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1057510-2143-CM26</t>
+          <t>2467-608-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21843,12 +21843,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21858,17 +21858,17 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -21877,13 +21877,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>4564.86</v>
+        <v>1066.14</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2467-608-CM26</t>
+          <t>2467-641-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21923,17 +21923,17 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -21942,13 +21942,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>1066.14</v>
+        <v>12518.48</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2467-641-CM26</t>
+          <t>1057510-2143-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21973,12 +21973,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21988,17 +21988,17 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -22007,7 +22007,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>12518.48</v>
+        <v>4564.86</v>
       </c>
     </row>
     <row r="341">
@@ -22399,7 +22399,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>3588-258-CM26</t>
+          <t>4594-490-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22424,12 +22424,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22458,13 +22458,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1731.16</v>
+        <v>830.28</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>4594-490-CM26</t>
+          <t>1700-56-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22489,12 +22489,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -22504,32 +22504,28 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Papeles Cono Sur Ltda.</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>78.437.580-3</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>830.28</v>
+        <v>2521.04</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1700-56-CM26</t>
+          <t>1059082-19-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22549,17 +22545,17 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -22569,28 +22565,32 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>Papeles Cono Sur Ltda.</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>78.437.580-3</t>
-        </is>
-      </c>
-      <c r="K349" t="inlineStr"/>
+          <t>77.461.733-7</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>2521.04</v>
+        <v>1182.61</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1059082-19-CM26</t>
+          <t>2724-466-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22615,12 +22615,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>NATIONAL PAPER SPA</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>78.085.327-1</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -22649,13 +22649,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>1182.61</v>
+        <v>4777.05</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2724-466-CM26</t>
+          <t>3588-258-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -22675,17 +22675,17 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -22695,17 +22695,17 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>NATIONAL PAPER SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>78.085.327-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -22714,7 +22714,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>4777.05</v>
+        <v>1731.16</v>
       </c>
     </row>
     <row r="352">
@@ -23675,7 +23675,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1051765-604-CM26</t>
+          <t>1069417-797-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -23700,12 +23700,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -23715,17 +23715,17 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -23734,13 +23734,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>785.6799999999999</v>
+        <v>1364.06</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1069417-797-CM26</t>
+          <t>1051765-604-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -23765,12 +23765,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -23780,17 +23780,17 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -23799,7 +23799,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>1364.06</v>
+        <v>785.6799999999999</v>
       </c>
     </row>
     <row r="369">
@@ -24065,7 +24065,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>3904-698-CM26</t>
+          <t>3904-707-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24124,13 +24124,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>768.45</v>
+        <v>1704.26</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>3904-707-CM26</t>
+          <t>3904-698-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24189,7 +24189,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>1704.26</v>
+        <v>768.45</v>
       </c>
     </row>
     <row r="375">
@@ -24711,7 +24711,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1057510-3114-CM26</t>
+          <t>4252-235-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -24736,12 +24736,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -24751,32 +24751,28 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K383" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr"/>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>2485.21</v>
+        <v>2713.58</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>4252-235-CM26</t>
+          <t>1534596-3-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -24801,12 +24797,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -24816,28 +24812,32 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K384" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>2713.58</v>
+        <v>1168.13</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1534596-3-CM26</t>
+          <t>1057510-3114-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -24862,12 +24862,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -24896,7 +24896,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1168.13</v>
+        <v>2485.21</v>
       </c>
     </row>
     <row r="386">
@@ -24967,7 +24967,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2727-693-CM26</t>
+          <t>1062448-1828-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -24992,12 +24992,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>61.931.800-5</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>CONSULTORIO GENERAL URBANO VIOLETA PARRA</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25007,28 +25007,32 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K387" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>1507.22</v>
+        <v>1995.08</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1062448-1828-CM26</t>
+          <t>2727-693-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25053,12 +25057,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>61.931.800-5</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VIOLETA PARRA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25068,26 +25072,22 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K388" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>1995.08</v>
+        <v>1507.22</v>
       </c>
     </row>
     <row r="389">
@@ -25223,7 +25223,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1375761-1499-CM26</t>
+          <t>2705-1315-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25243,17 +25243,17 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25282,13 +25282,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>3592.15</v>
+        <v>1282.77</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2705-1315-CM26</t>
+          <t>1375761-1499-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25308,17 +25308,17 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25347,7 +25347,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>1282.77</v>
+        <v>3592.15</v>
       </c>
     </row>
     <row r="393">
@@ -25414,7 +25414,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1057506-4529-CM26</t>
+          <t>1057506-4532-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -25454,12 +25454,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL GMA SPA</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.053.654-5</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
@@ -25473,13 +25473,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>1881.64</v>
+        <v>782.08</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1057506-4532-CM26</t>
+          <t>1057506-4529-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25519,12 +25519,12 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>COMERCIAL GMA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>77.053.654-5</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -25538,7 +25538,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>782.08</v>
+        <v>1881.64</v>
       </c>
     </row>
     <row r="396">
@@ -25930,7 +25930,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>3904-951-CM26</t>
+          <t>1059082-54-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -25955,12 +25955,12 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -25970,12 +25970,12 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
@@ -25989,13 +25989,13 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>815.63</v>
+        <v>8810.82</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>1059082-55-CM26</t>
+          <t>1059082-53-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -26035,28 +26035,32 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>76.195.957-3</t>
-        </is>
-      </c>
-      <c r="K403" t="inlineStr"/>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>4148.1</v>
+        <v>1817.98</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1059082-53-CM26</t>
+          <t>1059082-55-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -26096,32 +26100,28 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
-        </is>
-      </c>
-      <c r="K404" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.195.957-3</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>1817.98</v>
+        <v>4148.1</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1059082-46-CM26</t>
+          <t>3904-951-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -26146,12 +26146,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -26161,12 +26161,12 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -26180,13 +26180,13 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>3798.13</v>
+        <v>815.63</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1059082-54-CM26</t>
+          <t>1059082-46-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26226,12 +26226,12 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -26245,7 +26245,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>8810.82</v>
+        <v>3798.13</v>
       </c>
     </row>
     <row r="407">
@@ -26316,7 +26316,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1057514-301-CM26</t>
+          <t>1057510-3510-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26336,17 +26336,17 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>61.607.006-1</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26356,28 +26356,32 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K408" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>2513.57</v>
+        <v>4964.74</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1057510-3510-CM26</t>
+          <t>1057514-301-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26397,17 +26401,17 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>61.607.006-1</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -26417,26 +26421,22 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K409" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr"/>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>4964.74</v>
+        <v>2513.57</v>
       </c>
     </row>
     <row r="410">
@@ -26572,7 +26572,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1062807-89-CM26</t>
+          <t>1057511-1380-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -26597,12 +26597,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -26612,12 +26612,12 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -26631,13 +26631,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>2376.43</v>
+        <v>889.89</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1062807-90-CM26</t>
+          <t>4173-265-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -26657,17 +26657,17 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -26677,17 +26677,17 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
@@ -26696,13 +26696,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>1000.4</v>
+        <v>1460.45</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>4173-265-CM26</t>
+          <t>1062807-90-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -26722,17 +26722,17 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -26742,17 +26742,17 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
@@ -26761,13 +26761,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>1460.45</v>
+        <v>1000.4</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1057511-1380-CM26</t>
+          <t>1062807-89-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -26792,12 +26792,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -26807,12 +26807,12 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
@@ -26826,7 +26826,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>889.89</v>
+        <v>2376.43</v>
       </c>
     </row>
     <row r="416">
@@ -26917,7 +26917,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -27152,6 +27152,1099 @@
       </c>
       <c r="M420" s="2" t="n">
         <v>2105.1</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>4596-922-CM26</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>69.140.801-9</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M421" s="2" t="n">
+        <v>2385.1</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>4173-297-CM26</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>69.140.100-6</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Quirihue</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M422" s="2" t="n">
+        <v>993.34</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>1057511-1562-CM26</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>61.607.003-7</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M423" s="2" t="n">
+        <v>876.63</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2467-1204-CM26</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M424" s="2" t="n">
+        <v>1171.14</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2467-1207-CM26</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M425" s="2" t="n">
+        <v>1108.82</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>4596-926-CM26</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>69.140.801-9</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>77.610.393-4</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M426" s="2" t="n">
+        <v>1993.68</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>4596-960-CM26</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>69.140.801-9</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M427" s="2" t="n">
+        <v>795.75</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>1057124-29-CM26</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>62.000.600-9</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M428" s="2" t="n">
+        <v>2670.72</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>3904-1120-CM26</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>69.141.200-8</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE BULNES</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M429" s="2" t="n">
+        <v>1071.28</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>1069417-1392-CM26</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>69.270.200-k</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>BLUE MIX SPA</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr"/>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M430" s="2" t="n">
+        <v>759.87</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>1069417-1416-CM26</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>69.270.200-k</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M431" s="2" t="n">
+        <v>2186.56</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>229-767-CM26</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>69.141.100-1</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>BLUE MIX SPA</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M432" s="2" t="n">
+        <v>1146.54</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>1057506-4758-CM26</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>61.602.194-K</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>COMERCIAL GMA SPA</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>77.053.654-5</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M433" s="2" t="n">
+        <v>807.48</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>4352-31-CM26</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>69.141.400-0</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>BLUE MIX SPA</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M434" s="2" t="n">
+        <v>11216.77</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>1113015-96-CM26</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>BAILEY GROUP SPA</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>77.638.992-7</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M435" s="2" t="n">
+        <v>857.24</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>3674-660-CM26</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>69.266.500-7</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M436" s="2" t="n">
+        <v>1209.77</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>1043046-112-CM26</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>62.000.450-2</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M437" s="2" t="n">
+        <v>732</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/nuble.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M438"/>
+  <dimension ref="A1:M439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17340,7 +17340,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2724-156-CM26</t>
+          <t>1057510-1114-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17360,17 +17360,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17380,32 +17380,28 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Distribuidora Colon </t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.176.425-k</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>2239.44</v>
+        <v>2164.57</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1057510-1114-CM26</t>
+          <t>2724-156-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17425,17 +17421,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17445,22 +17441,26 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribuidora Colon </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>76.176.425-k</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>2164.57</v>
+        <v>2239.44</v>
       </c>
     </row>
     <row r="270">
@@ -17722,7 +17722,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>4596-130-CM26</t>
+          <t>4596-129-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17742,7 +17742,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -17781,13 +17781,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1472.3</v>
+        <v>772.8200000000001</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>4596-129-CM26</t>
+          <t>4596-130-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17807,7 +17807,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -17846,7 +17846,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>772.8200000000001</v>
+        <v>1472.3</v>
       </c>
     </row>
     <row r="276">
@@ -18742,7 +18742,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1057506-3922-CM26</t>
+          <t>1069417-325-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18767,12 +18767,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18782,32 +18782,28 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
-        </is>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1271.5</v>
+        <v>1194.66</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1069417-325-CM26</t>
+          <t>1057506-3922-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18832,12 +18828,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18847,22 +18843,26 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr"/>
+          <t>77.638.992-7</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1194.66</v>
+        <v>1271.5</v>
       </c>
     </row>
     <row r="292">
@@ -18994,7 +18994,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1069417-365-CM26</t>
+          <t>4596-237-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19014,17 +19014,17 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19034,17 +19034,17 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -19053,13 +19053,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>3473.23</v>
+        <v>1095.04</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4596-237-CM26</t>
+          <t>2724-275-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19079,17 +19079,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -19118,13 +19118,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1095.04</v>
+        <v>2198.99</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2724-275-CM26</t>
+          <t>1035180-16-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19144,17 +19144,17 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19164,32 +19164,28 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2198.99</v>
+        <v>1683.26</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1035180-16-CM26</t>
+          <t>1069417-365-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19209,17 +19205,17 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19229,22 +19225,26 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr"/>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1683.26</v>
+        <v>3473.23</v>
       </c>
     </row>
     <row r="298">
@@ -19770,7 +19770,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>3904-323-CM26</t>
+          <t>1057511-579-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19790,17 +19790,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19829,13 +19829,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>940.51</v>
+        <v>809.36</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1057511-579-CM26</t>
+          <t>3904-323-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19855,17 +19855,17 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19894,7 +19894,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>809.36</v>
+        <v>940.51</v>
       </c>
     </row>
     <row r="308">
@@ -19961,7 +19961,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>4596-257-CM26</t>
+          <t>1057510-1616-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19981,17 +19981,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -20001,17 +20001,17 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -20020,13 +20020,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>868.83</v>
+        <v>2050.68</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>4596-256-CM26</t>
+          <t>4252-126-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20051,12 +20051,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -20066,12 +20066,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -20085,13 +20085,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>868.83</v>
+        <v>3302.37</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>3747-114-CM26</t>
+          <t>4596-257-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20111,17 +20111,17 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>69.141.300-4</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -20131,17 +20131,17 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -20150,13 +20150,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>843.86</v>
+        <v>868.83</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>4252-126-CM26</t>
+          <t>4596-256-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20181,12 +20181,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20196,12 +20196,12 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -20215,13 +20215,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>3302.37</v>
+        <v>868.83</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1057510-1616-CM26</t>
+          <t>3747-114-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20246,12 +20246,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>69.141.300-4</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>I MUNICIPALIDAD DE SAN IGNACIO</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20261,17 +20261,17 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -20280,7 +20280,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>2050.68</v>
+        <v>843.86</v>
       </c>
     </row>
     <row r="314">
@@ -20664,7 +20664,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>4173-127-CM26</t>
+          <t>3590-79-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -20684,17 +20684,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -20704,17 +20704,17 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO LAGOS LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>77.547.396-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -20723,13 +20723,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>929.78</v>
+        <v>1116.06</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>3590-79-CM26</t>
+          <t>4173-127-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -20749,17 +20749,17 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20769,17 +20769,17 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LIBRERÍA GIORGIO LAGOS LIMITADA</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.547.396-7</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -20788,13 +20788,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1116.06</v>
+        <v>929.78</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>5615-292-CM26</t>
+          <t>1060500-12-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20819,12 +20819,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>69.141.700-K</t>
+          <t>62.000.510-k</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de El Carmen</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20834,17 +20834,17 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -20853,13 +20853,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>3334.53</v>
+        <v>2044.48</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1060500-12-CM26</t>
+          <t>5615-292-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20884,12 +20884,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>62.000.510-k</t>
+          <t>69.141.700-K</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20899,17 +20899,17 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -20918,7 +20918,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>2044.48</v>
+        <v>3334.53</v>
       </c>
     </row>
     <row r="324">
@@ -20985,7 +20985,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1057514-182-CM26</t>
+          <t>1040758-70-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21010,12 +21010,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>61.607.006-1</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -21044,13 +21044,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>1709.02</v>
+        <v>2177.38</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1040758-70-CM26</t>
+          <t>1057514-182-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21075,12 +21075,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>61.607.006-1</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21090,12 +21090,12 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -21109,13 +21109,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>2177.38</v>
+        <v>1709.02</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1069417-548-CM26</t>
+          <t>1059082-12-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21140,12 +21140,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21155,28 +21155,32 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K327" t="inlineStr"/>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1110.7</v>
+        <v>960.8200000000001</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1059082-12-CM26</t>
+          <t>1069417-548-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21201,12 +21205,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21216,26 +21220,22 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
-        </is>
-      </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>960.8200000000001</v>
+        <v>1110.7</v>
       </c>
     </row>
     <row r="329">
@@ -21562,7 +21562,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>4367-256-CM26</t>
+          <t>1057511-726-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21587,12 +21587,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>61.972.800-9</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21602,28 +21602,32 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1262.51</v>
+        <v>849.83</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1057511-726-CM26</t>
+          <t>4367-257-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21648,12 +21652,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>61.972.800-9</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -21663,17 +21667,17 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -21682,7 +21686,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>849.83</v>
+        <v>819.63</v>
       </c>
     </row>
     <row r="336">
@@ -21753,7 +21757,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>4596-427-CM26</t>
+          <t>4367-256-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -21778,12 +21782,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>61.972.800-9</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21793,32 +21797,28 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1779.1</v>
+        <v>1262.51</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>4367-257-CM26</t>
+          <t>4596-427-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21843,12 +21843,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.972.800-9</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21858,17 +21858,17 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -21877,7 +21877,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>819.63</v>
+        <v>1779.1</v>
       </c>
     </row>
     <row r="339">
@@ -23675,7 +23675,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>3904-598-CM26</t>
+          <t>1051765-604-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -23695,17 +23695,17 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -23715,17 +23715,17 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -23734,7 +23734,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>946.6</v>
+        <v>785.6799999999999</v>
       </c>
     </row>
     <row r="368">
@@ -23805,7 +23805,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1051765-604-CM26</t>
+          <t>3904-598-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -23825,17 +23825,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -23845,17 +23845,17 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -23864,7 +23864,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>785.6799999999999</v>
+        <v>946.6</v>
       </c>
     </row>
     <row r="370">
@@ -24000,7 +24000,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2727-606-CM26</t>
+          <t>4120-186-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24020,17 +24020,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.140.301-7</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -24040,17 +24040,17 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -24059,13 +24059,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1045.63</v>
+        <v>772.0599999999999</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>4120-186-CM26</t>
+          <t>2727-606-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24085,17 +24085,17 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>69.140.301-7</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -24105,17 +24105,17 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -24124,13 +24124,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>772.0599999999999</v>
+        <v>1045.63</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>3904-707-CM26</t>
+          <t>3904-698-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24189,13 +24189,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>1704.26</v>
+        <v>768.45</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>3904-698-CM26</t>
+          <t>3904-707-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24254,7 +24254,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>768.45</v>
+        <v>1704.26</v>
       </c>
     </row>
     <row r="376">
@@ -24711,7 +24711,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>4596-695-CM26</t>
+          <t>1534596-3-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -24736,12 +24736,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>69.140.801-9</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -24751,17 +24751,17 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -24770,13 +24770,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>1755.05</v>
+        <v>1168.13</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>4252-235-CM26</t>
+          <t>1057510-3114-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -24801,12 +24801,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>69.140.700-4</t>
+          <t>61.607.002-9</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -24816,28 +24816,32 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K384" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>2713.58</v>
+        <v>2485.21</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1534596-3-CM26</t>
+          <t>4596-695-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -24862,12 +24866,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>69.140.801-9</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -24877,17 +24881,17 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -24896,13 +24900,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1168.13</v>
+        <v>1755.05</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1057510-3114-CM26</t>
+          <t>4252-235-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -24927,12 +24931,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.607.002-9</t>
+          <t>69.140.700-4</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE SAN CARLOS DR BENICIO ARZOLA MEDIN</t>
+          <t>I MUNICIPALIDAD DE SAN FABIAN</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -24942,32 +24946,28 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K386" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>2485.21</v>
+        <v>2713.58</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1233616-1492-CM26</t>
+          <t>1062448-1828-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -24992,12 +24992,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>61.931.800-5</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>CONSULTORIO GENERAL URBANO VIOLETA PARRA</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25026,13 +25026,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>2628.57</v>
+        <v>1995.08</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1062448-1828-CM26</t>
+          <t>2727-693-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25057,12 +25057,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>61.931.800-5</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VIOLETA PARRA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25072,32 +25072,28 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K388" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>1995.08</v>
+        <v>1507.22</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2727-693-CM26</t>
+          <t>1233616-1492-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25122,12 +25118,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25137,22 +25133,26 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
-        </is>
-      </c>
-      <c r="K389" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>1507.22</v>
+        <v>2628.57</v>
       </c>
     </row>
     <row r="390">
@@ -25288,7 +25288,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2705-1315-CM26</t>
+          <t>1375761-1499-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25308,17 +25308,17 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25347,13 +25347,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>1282.77</v>
+        <v>3592.15</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1375761-1499-CM26</t>
+          <t>2705-1315-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25373,17 +25373,17 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -25412,7 +25412,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>3592.15</v>
+        <v>1282.77</v>
       </c>
     </row>
     <row r="394">
@@ -25479,7 +25479,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1057506-4532-CM26</t>
+          <t>1057506-4529-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25519,12 +25519,12 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>COMERCIAL GMA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>77.053.654-5</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -25538,13 +25538,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>782.08</v>
+        <v>1881.64</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1057506-4529-CM26</t>
+          <t>1057506-4532-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25584,12 +25584,12 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL GMA SPA</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.053.654-5</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -25603,7 +25603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>1881.64</v>
+        <v>782.08</v>
       </c>
     </row>
     <row r="397">
@@ -25800,7 +25800,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>4594-669-CM26</t>
+          <t>2467-1089-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -25825,12 +25825,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -25840,17 +25840,17 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
@@ -25859,13 +25859,13 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>1349.79</v>
+        <v>1829.09</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2467-1089-CM26</t>
+          <t>4594-669-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -25890,12 +25890,12 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -25905,17 +25905,17 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -25924,7 +25924,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1829.09</v>
+        <v>1349.79</v>
       </c>
     </row>
     <row r="402">
@@ -25995,7 +25995,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>1059082-54-CM26</t>
+          <t>1059082-46-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -26035,12 +26035,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -26054,13 +26054,13 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>8810.82</v>
+        <v>3798.13</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1059082-53-CM26</t>
+          <t>1059082-54-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -26080,7 +26080,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -26100,17 +26100,17 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -26119,7 +26119,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>1817.98</v>
+        <v>8810.82</v>
       </c>
     </row>
     <row r="405">
@@ -26251,7 +26251,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1059082-46-CM26</t>
+          <t>1059082-53-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26271,7 +26271,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -26291,17 +26291,17 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -26310,7 +26310,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>3798.13</v>
+        <v>1817.98</v>
       </c>
     </row>
     <row r="408">
@@ -26637,7 +26637,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1057511-1380-CM26</t>
+          <t>4173-265-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -26657,17 +26657,17 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.607.003-7</t>
+          <t>69.140.100-6</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -26677,17 +26677,17 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
@@ -26696,13 +26696,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>889.89</v>
+        <v>1460.45</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>4173-265-CM26</t>
+          <t>1062807-90-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -26722,17 +26722,17 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -26742,17 +26742,17 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
@@ -26761,13 +26761,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>1460.45</v>
+        <v>1000.4</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1062807-90-CM26</t>
+          <t>1062807-89-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -26826,13 +26826,13 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1000.4</v>
+        <v>2376.43</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1062807-89-CM26</t>
+          <t>1057511-1380-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -26857,12 +26857,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>61.607.003-7</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -26872,12 +26872,12 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
@@ -26891,7 +26891,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>2376.43</v>
+        <v>889.89</v>
       </c>
     </row>
     <row r="417">
@@ -28250,65 +28250,126 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
+          <t>1113015-98-CM26</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>BLUE MIX SPA</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>77.283.950-2</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M438" s="2" t="n">
+        <v>741.9</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
           <t>1043046-112-CM26</t>
         </is>
       </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>2239-16-LR24</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr">
+      <c r="D439" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
         <is>
           <t>62.000.450-2</t>
         </is>
       </c>
-      <c r="G438" t="inlineStr">
+      <c r="G439" t="inlineStr">
         <is>
           <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ÑUBLE</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I438" t="inlineStr">
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
         </is>
       </c>
-      <c r="J438" t="inlineStr">
+      <c r="J439" t="inlineStr">
         <is>
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr">
+      <c r="K439" t="inlineStr">
         <is>
           <t>Antofagasta</t>
         </is>
       </c>
-      <c r="L438" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M438" s="2" t="n">
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M439" s="2" t="n">
         <v>732</v>
       </c>
     </row>
